--- a/data/raw/benv_exports/dermatite_nodulare_contagiosa_2026_italia.xlsx
+++ b/data/raw/benv_exports/dermatite_nodulare_contagiosa_2026_italia.xlsx
@@ -589,7 +589,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>84397</v>
+        <v>85538</v>
       </c>
       <c r="B7" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -598,13 +598,13 @@
         <v>E</v>
       </c>
       <c r="D7" t="str">
-        <v>28/04/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="E7" t="str">
-        <v>28/04/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="F7" t="str">
-        <v>15/05/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -613,10 +613,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I7" t="str">
-        <v>BALLAO</v>
+        <v>SAMUGHEO</v>
       </c>
       <c r="J7" t="str">
-        <v>SU</v>
+        <v>OR</v>
       </c>
       <c r="K7" t="str">
         <v>SARDEGNA</v>
@@ -624,7 +624,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>84600</v>
+        <v>84397</v>
       </c>
       <c r="B8" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -633,14 +633,14 @@
         <v>E</v>
       </c>
       <c r="D8" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="E8" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="F8" t="str">
         <v>15/05/2026</v>
       </c>
-      <c r="E8" t="str">
-        <v>14/05/2026</v>
-      </c>
-      <c r="F8" t="str">
-        <v>19/05/2026</v>
-      </c>
       <c r="G8" t="str">
         <v/>
       </c>
@@ -648,7 +648,7 @@
         <v>BOVINO</v>
       </c>
       <c r="I8" t="str">
-        <v>MURAVERA</v>
+        <v>BALLAO</v>
       </c>
       <c r="J8" t="str">
         <v>SU</v>
@@ -659,22 +659,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>85538</v>
+        <v>84671</v>
       </c>
       <c r="B9" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C9" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D9" t="str">
-        <v>08/07/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="E9" t="str">
-        <v>08/07/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>-</v>
+        <v>14/07/2026</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -683,10 +683,10 @@
         <v>BOVINO</v>
       </c>
       <c r="I9" t="str">
-        <v>SAMUGHEO</v>
+        <v>SAN VITO</v>
       </c>
       <c r="J9" t="str">
-        <v>OR</v>
+        <v>SU</v>
       </c>
       <c r="K9" t="str">
         <v>SARDEGNA</v>
@@ -694,22 +694,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>84901</v>
+        <v>84600</v>
       </c>
       <c r="B10" t="str">
         <v>FOCOLAIO CLINICO</v>
       </c>
       <c r="C10" t="str">
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="D10" t="str">
-        <v>03/06/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="E10" t="str">
-        <v>30/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="F10" t="str">
-        <v>-</v>
+        <v>19/05/2026</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -718,7 +718,7 @@
         <v>BOVINO</v>
       </c>
       <c r="I10" t="str">
-        <v>ESCALAPLANO</v>
+        <v>MURAVERA</v>
       </c>
       <c r="J10" t="str">
         <v>SU</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>84671</v>
+        <v>84901</v>
       </c>
       <c r="B11" t="str">
         <v>FOCOLAIO CLINICO</v>
@@ -738,10 +738,10 @@
         <v>C</v>
       </c>
       <c r="D11" t="str">
-        <v>21/05/2026</v>
+        <v>03/06/2026</v>
       </c>
       <c r="E11" t="str">
-        <v>20/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="F11" t="str">
         <v>-</v>
@@ -753,7 +753,7 @@
         <v>BOVINO</v>
       </c>
       <c r="I11" t="str">
-        <v>SAN VITO</v>
+        <v>ESCALAPLANO</v>
       </c>
       <c r="J11" t="str">
         <v>SU</v>
